--- a/TEST_ascot_tipping_scoresheet.xlsx
+++ b/TEST_ascot_tipping_scoresheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://koresystems-my.sharepoint.com/personal/amye_dyrmishi_koresystems_com/Documents/Documents/Events/Ascot Networking Day 18.06.2026/Tipping Competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="201" documentId="8_{B904B16F-77D3-4252-AE0A-75A02AA69DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC4B41CB-75D0-43A7-ABC4-B69CC48BE5B8}"/>
+  <xr:revisionPtr revIDLastSave="205" documentId="8_{B904B16F-77D3-4252-AE0A-75A02AA69DF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{10706B68-A791-48EF-ABAD-410D7990986E}"/>
   <bookViews>
-    <workbookView xWindow="2376" yWindow="2136" windowWidth="13836" windowHeight="7140" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guest List" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="192">
   <si>
     <t>CONFIRMED GUESTS</t>
   </si>
@@ -944,23 +944,23 @@
     <xf numFmtId="0" fontId="21" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1237,16 +1237,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.850000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="37"/>
+      <c r="A1" s="38" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="38"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="38"/>
+      <c r="B2" s="39"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1639,26 +1639,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
     </row>
     <row r="2" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
+      <c r="B2" s="37"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
     </row>
     <row r="3" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
@@ -2215,26 +2215,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
     </row>
     <row r="2" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
     </row>
     <row r="3" spans="1:7" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
@@ -2286,7 +2286,9 @@
       <c r="A5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4"/>
+      <c r="B5" s="4" t="s">
+        <v>126</v>
+      </c>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
@@ -2338,15 +2340,15 @@
       <c r="G9" s="4"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="42" t="s">
+      <c r="A11" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2445,42 +2447,42 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
+      <c r="G1" s="36"/>
+      <c r="H1" s="36"/>
+      <c r="I1" s="36"/>
+      <c r="J1" s="36"/>
+      <c r="K1" s="36"/>
+      <c r="L1" s="36"/>
+      <c r="M1" s="36"/>
+      <c r="N1" s="36"/>
+      <c r="O1" s="36"/>
     </row>
     <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="41"/>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
     </row>
     <row r="3" spans="1:15" ht="22.8" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
@@ -2543,20 +2545,26 @@
         <f>IF(C4="","",IF(UPPER(C4)=UPPER('Race Results'!B4),10,IF(UPPER(C4)=UPPER('Race Results'!C4),6,IF(UPPER(C4)=UPPER('Race Results'!D4),4,IF(UPPER(C4)=UPPER('Race Results'!E4),3,IF(UPPER(C4)=UPPER('Race Results'!F4),2,IF(UPPER(C4)=UPPER('Race Results'!G4),1,0)))))))</f>
         <v>10</v>
       </c>
-      <c r="E4" s="15"/>
-      <c r="F4" s="16" t="str">
+      <c r="E4" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="16">
         <f>IF(E4="","",IF(UPPER(E4)=UPPER('Race Results'!B5),10,IF(UPPER(E4)=UPPER('Race Results'!C5),6,IF(UPPER(E4)=UPPER('Race Results'!D5),4,IF(UPPER(E4)=UPPER('Race Results'!E5),3,IF(UPPER(E4)=UPPER('Race Results'!F5),2,IF(UPPER(E4)=UPPER('Race Results'!G5),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="G4" s="15"/>
-      <c r="H4" s="16" t="str">
+        <v>10</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="H4" s="16">
         <f>IF(G4="","",IF(UPPER(G4)=UPPER('Race Results'!B6),10,IF(UPPER(G4)=UPPER('Race Results'!C6),6,IF(UPPER(G4)=UPPER('Race Results'!D6),4,IF(UPPER(G4)=UPPER('Race Results'!E6),3,IF(UPPER(G4)=UPPER('Race Results'!F6),2,IF(UPPER(G4)=UPPER('Race Results'!G6),1,0)))))))</f>
-        <v/>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="16" t="str">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="J4" s="16">
         <f>IF(I4="","",IF(UPPER(I4)=UPPER('Race Results'!B7),10,IF(UPPER(I4)=UPPER('Race Results'!C7),6,IF(UPPER(I4)=UPPER('Race Results'!D7),4,IF(UPPER(I4)=UPPER('Race Results'!E7),3,IF(UPPER(I4)=UPPER('Race Results'!F7),2,IF(UPPER(I4)=UPPER('Race Results'!G7),1,0)))))))</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="K4" s="15"/>
       <c r="L4" s="16" t="str">
@@ -2570,7 +2578,7 @@
       </c>
       <c r="O4" s="17">
         <f t="shared" ref="O4:O33" si="0">IF(COUNTA(D4,F4,H4,J4,L4,N4)=0,"",SUM(D4,F4,H4,J4,L4,N4))</f>
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="15.6" x14ac:dyDescent="0.3">
@@ -3943,12 +3951,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="42" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
+      <c r="B1" s="42"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="42"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
@@ -3974,11 +3982,11 @@
       </c>
       <c r="C3" s="20">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$O$4:$O$33,1),"")</f>
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D3" s="21">
         <f ca="1">IFERROR(COUNTIF(OFFSET('Picks &amp; Scores'!$D$4:$N$33,MATCH(C3,'Picks &amp; Scores'!$O$4:$O$33,0)-1,0,1,11),10),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.3">
@@ -3987,7 +3995,7 @@
       </c>
       <c r="B4" s="19" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$O$4:$O$33,2),'Picks &amp; Scores'!$O$4:$O$33,0)),"")</f>
-        <v>Sophie Mitchel</v>
+        <v>Olivia Chambers</v>
       </c>
       <c r="C4" s="20">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$O$4:$O$33,2),"")</f>
@@ -4004,7 +4012,7 @@
       </c>
       <c r="B5" s="19" t="str">
         <f>IFERROR(INDEX('Picks &amp; Scores'!$B$4:$B$33,MATCH(LARGE('Picks &amp; Scores'!$O$4:$O$33,3),'Picks &amp; Scores'!$O$4:$O$33,0)),"")</f>
-        <v>Sophie Mitchel</v>
+        <v>Olivia Chambers</v>
       </c>
       <c r="C5" s="20">
         <f>IFERROR(LARGE('Picks &amp; Scores'!$O$4:$O$33,3),"")</f>
@@ -4495,14 +4503,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="36"/>
     </row>
     <row r="3" spans="1:6" ht="17.399999999999999" x14ac:dyDescent="0.35">
       <c r="A3" s="43" t="s">
